--- a/plotting_and_statistics_script_with_demo_data/output_files_of_py_script/2025-12-03 08_15_00_statistics_TEMP_LOG_demo_data.xlsx
+++ b/plotting_and_statistics_script_with_demo_data/output_files_of_py_script/2025-12-03 08_15_00_statistics_TEMP_LOG_demo_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -430,29 +418,29 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Vbatt</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>TMP1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>TMP2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>duration [d]</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -466,12 +454,12 @@
       <c r="D2" t="n">
         <v>202</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
@@ -485,12 +473,12 @@
       <c r="D3" t="n">
         <v>25.44920792079208</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>min</t>
         </is>
@@ -504,12 +492,12 @@
       <c r="D4" t="n">
         <v>20.3</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -523,12 +511,12 @@
       <c r="D5" t="n">
         <v>21.72</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -542,12 +530,12 @@
       <c r="D6" t="n">
         <v>25.56</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -561,12 +549,12 @@
       <c r="D7" t="n">
         <v>27.4275</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>max</t>
         </is>
@@ -580,12 +568,12 @@
       <c r="D8" t="n">
         <v>34.88</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>std</t>
         </is>
@@ -599,7 +587,7 @@
       <c r="D9" t="n">
         <v>3.904684310990347</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="1" t="n">
         <v>0.7013888888888888</v>
       </c>
     </row>
